--- a/public/templates/specialists_template.xlsx
+++ b/public/templates/specialists_template.xlsx
@@ -11,21 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
-  <si>
-    <t>Only the first two columns are required — the rest is optional and can be set later in the wizard.</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>subject</t>
-  </si>
-  <si>
-    <t>working days (optional)</t>
-  </si>
-  <si>
-    <t>room (optional)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t>Teacher Name</t>
+  </si>
+  <si>
+    <t>Specialist (Art, Tech, PE...)</t>
   </si>
   <si>
     <t>Swanson</t>
@@ -34,26 +25,17 @@
     <t>Art</t>
   </si>
   <si>
-    <t>Mon,Tue,Wed,Thu,Fri</t>
-  </si>
-  <si>
-    <t>D-1</t>
-  </si>
-  <si>
     <t>Mike</t>
   </si>
   <si>
     <t>PE</t>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -62,19 +44,9 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <i/>
-      <color rgb="FF6B7280"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -103,15 +75,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -451,69 +417,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B3" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
